--- a/src/fnschool/exam/data/parental_emails.xlsx
+++ b/src/fnschool/exam/data/parental_emails.xlsx
@@ -11,13 +11,18 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="R1C1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
-    <author>Larry Wei</author>
+    <author>Wei Larry</author>
   </authors>
   <commentList>
     <comment ref="B2" authorId="0">
@@ -35,6 +40,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">;”</t>
         </r>
@@ -43,6 +49,7 @@
             <sz val="10"/>
             <rFont val="Noto Sans CJK SC"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">、“</t>
         </r>
@@ -51,6 +58,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">/”</t>
         </r>
@@ -59,6 +67,7 @@
             <sz val="10"/>
             <rFont val="Noto Sans CJK SC"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">、“、”、“</t>
         </r>
@@ -67,6 +76,7 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">|”</t>
         </r>
@@ -75,6 +85,7 @@
             <sz val="10"/>
             <rFont val="Noto Sans CJK SC"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">、换行 隔开。</t>
         </r>
@@ -142,10 +153,10 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+  <fonts count="8">
+    <font>
+      <sz val="10"/>
+      <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
     <font>
@@ -162,11 +173,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -174,9 +180,22 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="12"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -226,11 +245,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -448,8 +467,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/src/fnschool/exam/data/parental_emails.xlsx
+++ b/src/fnschool/exam/data/parental_emails.xlsx
@@ -95,69 +95,17 @@
 </comments>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t xml:space="preserve">爸爸</t>
-  </si>
-  <si>
-    <t xml:space="preserve">妈妈</t>
-  </si>
-  <si>
-    <t xml:space="preserve">爷爷</t>
-  </si>
-  <si>
-    <t xml:space="preserve">奶奶</t>
-  </si>
-  <si>
-    <t xml:space="preserve">外公</t>
-  </si>
-  <si>
-    <t xml:space="preserve">外婆</t>
-  </si>
-  <si>
-    <t xml:space="preserve">叔叔</t>
-  </si>
-  <si>
-    <t xml:space="preserve">阿姨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">姑妈</t>
-  </si>
-  <si>
-    <t xml:space="preserve">姑爹</t>
-  </si>
-  <si>
-    <t xml:space="preserve">姨妈</t>
-  </si>
-  <si>
-    <t xml:space="preserve">姨父</t>
-  </si>
-  <si>
-    <t xml:space="preserve">亲戚</t>
-  </si>
-  <si>
-    <t xml:space="preserve">朋友</t>
-  </si>
-  <si>
-    <t xml:space="preserve">家长</t>
-  </si>
-  <si>
-    <t xml:space="preserve">监护人</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -173,11 +121,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -187,13 +130,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Noto Sans CJK SC"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -245,11 +187,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -376,93 +318,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:A17"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="2" width="11.53"/>
   </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
